--- a/XLS/SCRAPE_youtube_single_video.xlsx
+++ b/XLS/SCRAPE_youtube_single_video.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,56 +427,74 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Figma MCP + Cursor: The New AI Design System Workflow</v>
+        <v>O Jeito Preguiçoso de Fazer Dinheiro com IA (2026)</v>
       </c>
       <c r="B2">
-        <v>102937</v>
+        <v>7986</v>
       </c>
       <c r="C2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Figma MCP and Cursor now make it possible to move from design to code much faster. In this video I show a simple workflow that connects your design system in Figma to a real project in Cursor, generates components, updates tokens, and keeps everything in sync. It is a practical setup you can use to speed up handoff, reduce manual work, and build cleaner UI with less effort.
-🔗 KEY LINKS
-📣 JOIN THE COMMUNITY: https://uicollective.co/ 
-❓ Why Join UI Collective Academy? Get access to premium courses, premium downloads, and so much more on the way (I am largely building this solo...trying to make design education available for all, support goes a long way!)
-AMIR'S CHANNEL:
-Channel: @amirmxt 
-Amir's community: https://buildshipmarket.com/
-↪️ Need a design system? (also included in the academy): https://collectivekit.co/
-🔗 OTHER VIDEOS
-Build a Design System: https://youtu.be/opTANvl9G1g
-Complex Design System Setup: https://youtu.be/L-tpK7Eeuow
-🔗 MORE LINKS
-@Figma  MCP Catalog: https://www.figma.com/mcp-catalog/
-Let us build or fix your design system: https://designsystemlabs.co/
-kirkland@uicollective.co 
-0:00 An Introduction
-0:52 Connecting Cursor &amp; Figma MCP
-3:38 AI Generation Technique
-5:08 Figma Variable and Design Token Intro
-6:21 Vibe-Coding Our Design Tokens
-12:33 Choosing Our Components
-13:22 Vibe-Coding Our Figma Components
-16:44 Previewing End Result
-#cursor #ai #figma</v>
+        <v xml:space="preserve">🏆 VOTE EM MIM NO PRÊMIO iBEST:
+→  https://elirigobeli.com/ibest
+📌 HOSPEDAGEM VPS NA HOSTINGER
+→ Use o CUPOM: ELIRIGOBELIAI (10% OFF)
+→ https://links.elirigobeli.com/hostinger-connector
+🔥Se inscreva para receber novidades:
+https://links.elirigobeli.com/lista
+LISNKS:
+Livro: https://links.elirigobeli.com/livro-o-maior-vendedor-do-mundo
+Artigo: https://www.stripeeconomics.com/p/the-age-of-the-solopreneur
+Você precisa assistir estes vídeos 👇🏻
+Crie Saas: https://youtu.be/JEESRkJ0fXA
+Crie Apps: https://youtu.be/nw3POEg8iYs
+Me segue no insta: @elirigobeli
+Nesse vídeo eu te mostro o jeito mais simples de criar um site com IA e colocar ele no ar, do zero, usando o Hostinger Connector direto no editor. Sem mexer em servidor, sem complicação: a IA cria, publica, gerencia a hospedagem e até o banco de dados conversando. Faço tudo na prática montando um site real do começo ao fim, pra você usar isso como uma renda extra criando sites pra negócios locais.
+Não é promessa de ficar rico, é o passo a passo honesto pra você conseguir seu primeiro cliente pagando.</v>
       </c>
       <c r="D2">
-        <v>1900</v>
+        <v>809</v>
       </c>
       <c r="E2" t="str">
-        <v>ai, figma, cursor</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>https://www.youtube.com/watch?v=09VgyFFLrOw</v>
+        <v>https://www.youtube.com/watch?v=KOVXOPnyym0</v>
       </c>
       <c r="G2">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="H2" t="str">
-        <v>2025-11-25T14:00:18.000Z</v>
+        <v>2026-07-04T16:15:08.000Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Quando as pessoas descobrirem que IA vai além do chat, o mundo conhecerá quem sa</v>
+      </c>
+      <c r="B3">
+        <v>1113</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Quando as pessoas descobrirem que IA vai além do chat, o mundo conhecerá quem saiu na frente. Eli</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>https://www.youtube.com/shorts/qMSJ6L36nhA</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-07-04T19:37:10.000Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>